--- a/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/BasicStructure.xlsx
+++ b/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/BasicStructure.xlsx
@@ -44,21 +44,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="sales_detail" displayName="sales_detail" ref="A1:C3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SalesDetail" displayName="SalesDetail" ref="A1:C3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
-    <x:tableColumn id="1" name="customer_id"/>
-    <x:tableColumn id="2" name="amount"/>
-    <x:tableColumn id="3" name="description"/>
+    <x:tableColumn id="1" name="CustomerId"/>
+    <x:tableColumn id="2" name="Amount"/>
+    <x:tableColumn id="3" name="Description"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="product_list" displayName="product_list" ref="A1:B2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ProductList" displayName="ProductList" ref="A1:B2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
-    <x:tableColumn id="1" name="id"/>
-    <x:tableColumn id="2" name="name"/>
+    <x:tableColumn id="1" name="Id"/>
+    <x:tableColumn id="2" name="Name"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -261,13 +261,13 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>customer_id</x:v>
+        <x:v>CustomerId</x:v>
       </x:c>
       <x:c r="B1" t="str">
-        <x:v>amount</x:v>
+        <x:v>Amount</x:v>
       </x:c>
       <x:c r="C1" t="str">
-        <x:v>description</x:v>
+        <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -306,10 +306,10 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>id</x:v>
+        <x:v>Id</x:v>
       </x:c>
       <x:c r="B1" t="str">
-        <x:v>name</x:v>
+        <x:v>Name</x:v>
       </x:c>
     </x:row>
     <x:row r="2">

--- a/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/BasicStructure.xlsx
+++ b/CSharp/SpreadSheetAsData.CodeGenerationのテスト/TestData/コード生成/BasicStructure.xlsx
@@ -44,9 +44,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SalesDetail" displayName="SalesDetail" ref="A1:C3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="sales_detail" displayName="sales_detail" ref="A1:C3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
-    <x:tableColumn id="1" name="CustomerId"/>
+    <x:tableColumn id="1" name="customer_id"/>
     <x:tableColumn id="2" name="Amount"/>
     <x:tableColumn id="3" name="Description"/>
   </x:tableColumns>
@@ -261,7 +261,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>CustomerId</x:v>
+        <x:v>customer_id</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Amount</x:v>
